--- a/data/raw/inventory/Week 36/Audio_Array/Imports (OrderPilot).xlsx
+++ b/data/raw/inventory/Week 36/Audio_Array/Imports (OrderPilot).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3065" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="746">
   <si>
     <t>SKU</t>
   </si>
@@ -2609,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G515"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3891,7 +3891,7 @@
         <v>555</v>
       </c>
       <c r="E56">
-        <v>2000</v>
+        <v>2040</v>
       </c>
       <c r="F56" t="s">
         <v>743</v>
@@ -4489,7 +4489,7 @@
         <v>581</v>
       </c>
       <c r="E82">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="F82" t="s">
         <v>743</v>
@@ -6317,19 +6317,19 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B162" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C162" t="s">
         <v>500</v>
       </c>
       <c r="D162" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E162">
-        <v>888</v>
+        <v>0</v>
       </c>
       <c r="F162" t="s">
         <v>743</v>
@@ -6340,16 +6340,16 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B163" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C163" t="s">
         <v>500</v>
       </c>
       <c r="D163" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -6363,16 +6363,16 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B164" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C164" t="s">
         <v>500</v>
       </c>
       <c r="D164" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -6386,16 +6386,16 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B165" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C165" t="s">
         <v>500</v>
       </c>
       <c r="D165" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -6409,16 +6409,16 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B166" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C166" t="s">
         <v>500</v>
       </c>
       <c r="D166" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -6432,16 +6432,16 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B167" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C167" t="s">
         <v>500</v>
       </c>
       <c r="D167" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -6455,16 +6455,16 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B168" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C168" t="s">
         <v>500</v>
       </c>
       <c r="D168" t="s">
-        <v>664</v>
+        <v>615</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -6478,16 +6478,16 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B169" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C169" t="s">
         <v>500</v>
       </c>
       <c r="D169" t="s">
-        <v>615</v>
+        <v>665</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -6501,16 +6501,16 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B170" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C170" t="s">
         <v>500</v>
       </c>
       <c r="D170" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -6524,16 +6524,16 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B171" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C171" t="s">
         <v>500</v>
       </c>
       <c r="D171" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -6547,19 +6547,19 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B172" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C172" t="s">
         <v>500</v>
       </c>
       <c r="D172" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F172" t="s">
         <v>743</v>
@@ -6570,19 +6570,19 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B173" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C173" t="s">
         <v>500</v>
       </c>
       <c r="D173" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E173">
-        <v>2000</v>
+        <v>1840</v>
       </c>
       <c r="F173" t="s">
         <v>743</v>
@@ -6593,19 +6593,19 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B174" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C174" t="s">
         <v>500</v>
       </c>
       <c r="D174" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E174">
-        <v>1840</v>
+        <v>0</v>
       </c>
       <c r="F174" t="s">
         <v>743</v>
@@ -6616,19 +6616,19 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B175" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C175" t="s">
         <v>500</v>
       </c>
       <c r="D175" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F175" t="s">
         <v>743</v>
@@ -6639,19 +6639,19 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B176" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C176" t="s">
         <v>500</v>
       </c>
       <c r="D176" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E176">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F176" t="s">
         <v>743</v>
@@ -6662,16 +6662,16 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B177" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C177" t="s">
         <v>500</v>
       </c>
       <c r="D177" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6685,19 +6685,19 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B178" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C178" t="s">
         <v>500</v>
       </c>
       <c r="D178" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F178" t="s">
         <v>743</v>
@@ -6708,19 +6708,19 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B179" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C179" t="s">
         <v>500</v>
       </c>
       <c r="D179" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E179">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F179" t="s">
         <v>743</v>
@@ -6731,19 +6731,19 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B180" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C180" t="s">
         <v>500</v>
       </c>
       <c r="D180" t="s">
-        <v>675</v>
+        <v>631</v>
       </c>
       <c r="E180">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F180" t="s">
         <v>743</v>
@@ -6754,16 +6754,16 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B181" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C181" t="s">
         <v>500</v>
       </c>
       <c r="D181" t="s">
-        <v>631</v>
+        <v>676</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6777,16 +6777,16 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B182" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C182" t="s">
         <v>500</v>
       </c>
       <c r="D182" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6800,19 +6800,19 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B183" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C183" t="s">
         <v>500</v>
       </c>
       <c r="D183" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E183">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F183" t="s">
         <v>743</v>
@@ -6823,16 +6823,16 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B184" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C184" t="s">
         <v>500</v>
       </c>
       <c r="D184" t="s">
-        <v>677</v>
+        <v>622</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6846,16 +6846,16 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B185" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C185" t="s">
         <v>500</v>
       </c>
       <c r="D185" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6869,16 +6869,16 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B186" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C186" t="s">
         <v>500</v>
       </c>
       <c r="D186" t="s">
-        <v>622</v>
+        <v>680</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6892,16 +6892,16 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B187" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C187" t="s">
         <v>500</v>
       </c>
       <c r="D187" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6915,16 +6915,16 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B188" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C188" t="s">
         <v>500</v>
       </c>
       <c r="D188" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6938,16 +6938,16 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B189" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C189" t="s">
         <v>500</v>
       </c>
       <c r="D189" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6961,16 +6961,16 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B190" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C190" t="s">
         <v>500</v>
       </c>
       <c r="D190" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6984,16 +6984,16 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B191" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C191" t="s">
         <v>500</v>
       </c>
       <c r="D191" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -7007,19 +7007,19 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B192" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C192" t="s">
         <v>500</v>
       </c>
       <c r="D192" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F192" t="s">
         <v>743</v>
@@ -7030,16 +7030,16 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B193" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C193" t="s">
         <v>500</v>
       </c>
       <c r="D193" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -7053,19 +7053,19 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B194" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C194" t="s">
         <v>500</v>
       </c>
       <c r="D194" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="E194">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F194" t="s">
         <v>743</v>
@@ -7076,16 +7076,16 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B195" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C195" t="s">
         <v>500</v>
       </c>
       <c r="D195" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -7099,16 +7099,16 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B196" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C196" t="s">
         <v>500</v>
       </c>
       <c r="D196" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -7122,16 +7122,16 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B197" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C197" t="s">
         <v>500</v>
       </c>
       <c r="D197" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -7145,16 +7145,16 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B198" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C198" t="s">
         <v>500</v>
       </c>
       <c r="D198" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -7168,16 +7168,16 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B199" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C199" t="s">
         <v>500</v>
       </c>
       <c r="D199" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -7191,16 +7191,16 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B200" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C200" t="s">
         <v>500</v>
       </c>
       <c r="D200" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -7214,16 +7214,16 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B201" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C201" t="s">
         <v>500</v>
       </c>
       <c r="D201" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -7237,16 +7237,16 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B202" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C202" t="s">
         <v>500</v>
       </c>
       <c r="D202" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -7260,16 +7260,16 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B203" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C203" t="s">
         <v>500</v>
       </c>
       <c r="D203" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -7283,16 +7283,16 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B204" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C204" t="s">
         <v>500</v>
       </c>
       <c r="D204" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -7306,16 +7306,16 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B205" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C205" t="s">
         <v>500</v>
       </c>
       <c r="D205" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -7329,16 +7329,16 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B206" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C206" t="s">
         <v>500</v>
       </c>
       <c r="D206" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -7352,16 +7352,16 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B207" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C207" t="s">
         <v>500</v>
       </c>
       <c r="D207" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7375,16 +7375,16 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B208" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C208" t="s">
         <v>500</v>
       </c>
       <c r="D208" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7398,16 +7398,16 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B209" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C209" t="s">
         <v>500</v>
       </c>
       <c r="D209" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7421,16 +7421,16 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B210" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C210" t="s">
         <v>500</v>
       </c>
       <c r="D210" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7444,16 +7444,16 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B211" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C211" t="s">
         <v>500</v>
       </c>
       <c r="D211" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7467,16 +7467,16 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B212" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C212" t="s">
         <v>500</v>
       </c>
       <c r="D212" t="s">
-        <v>704</v>
+        <v>632</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7490,16 +7490,16 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B213" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C213" t="s">
         <v>500</v>
       </c>
       <c r="D213" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7513,16 +7513,16 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B214" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C214" t="s">
         <v>500</v>
       </c>
       <c r="D214" t="s">
-        <v>632</v>
+        <v>707</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7536,16 +7536,16 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B215" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C215" t="s">
         <v>500</v>
       </c>
       <c r="D215" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7559,16 +7559,16 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B216" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C216" t="s">
         <v>500</v>
       </c>
       <c r="D216" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7582,16 +7582,16 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B217" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C217" t="s">
         <v>500</v>
       </c>
       <c r="D217" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7605,16 +7605,16 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B218" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C218" t="s">
         <v>500</v>
       </c>
       <c r="D218" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7628,19 +7628,19 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B219" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C219" t="s">
         <v>500</v>
       </c>
       <c r="D219" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E219">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F219" t="s">
         <v>743</v>
@@ -7651,16 +7651,16 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B220" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C220" t="s">
         <v>500</v>
       </c>
       <c r="D220" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7674,16 +7674,16 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B221" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C221" t="s">
         <v>500</v>
       </c>
       <c r="D221" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7697,16 +7697,16 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B222" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C222" t="s">
         <v>500</v>
       </c>
       <c r="D222" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7720,16 +7720,16 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B223" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C223" t="s">
         <v>500</v>
       </c>
       <c r="D223" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7743,16 +7743,16 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B224" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C224" t="s">
         <v>500</v>
       </c>
       <c r="D224" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7766,16 +7766,16 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B225" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C225" t="s">
         <v>500</v>
       </c>
       <c r="D225" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7789,19 +7789,19 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B226" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C226" t="s">
         <v>500</v>
       </c>
       <c r="D226" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E226">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F226" t="s">
         <v>743</v>
@@ -7812,19 +7812,19 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B227" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C227" t="s">
         <v>500</v>
       </c>
       <c r="D227" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E227">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F227" t="s">
         <v>743</v>
@@ -7835,19 +7835,19 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B228" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C228" t="s">
         <v>500</v>
       </c>
       <c r="D228" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E228">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F228" t="s">
         <v>743</v>
@@ -7858,19 +7858,19 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B229" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C229" t="s">
         <v>500</v>
       </c>
       <c r="D229" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E229">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F229" t="s">
         <v>743</v>
@@ -7881,16 +7881,16 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B230" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C230" t="s">
         <v>500</v>
       </c>
       <c r="D230" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7904,16 +7904,16 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B231" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C231" t="s">
         <v>500</v>
       </c>
       <c r="D231" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7927,16 +7927,16 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B232" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C232" t="s">
         <v>500</v>
       </c>
       <c r="D232" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7950,16 +7950,16 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B233" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C233" t="s">
         <v>500</v>
       </c>
       <c r="D233" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7973,16 +7973,16 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B234" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C234" t="s">
         <v>500</v>
       </c>
       <c r="D234" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7996,16 +7996,16 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B235" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C235" t="s">
         <v>500</v>
       </c>
       <c r="D235" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -8019,16 +8019,16 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B236" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C236" t="s">
         <v>500</v>
       </c>
       <c r="D236" t="s">
-        <v>727</v>
+        <v>670</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -8042,16 +8042,13 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" t="s">
-        <v>238</v>
-      </c>
-      <c r="B237" t="s">
-        <v>491</v>
+        <v>240</v>
       </c>
       <c r="C237" t="s">
         <v>500</v>
       </c>
       <c r="D237" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -8065,16 +8062,13 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" t="s">
-        <v>239</v>
-      </c>
-      <c r="B238" t="s">
-        <v>492</v>
+        <v>241</v>
       </c>
       <c r="C238" t="s">
         <v>500</v>
       </c>
       <c r="D238" t="s">
-        <v>670</v>
+        <v>730</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -8088,13 +8082,13 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C239" t="s">
         <v>500</v>
       </c>
       <c r="D239" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8108,13 +8102,13 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C240" t="s">
         <v>500</v>
       </c>
       <c r="D240" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8128,13 +8122,13 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C241" t="s">
         <v>500</v>
       </c>
       <c r="D241" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8148,13 +8142,13 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C242" t="s">
         <v>500</v>
       </c>
       <c r="D242" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8168,13 +8162,13 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C243" t="s">
         <v>500</v>
       </c>
       <c r="D243" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8188,13 +8182,13 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C244" t="s">
         <v>500</v>
       </c>
       <c r="D244" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8208,13 +8202,13 @@
     </row>
     <row r="245" spans="1:7">
       <c r="A245" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C245" t="s">
         <v>500</v>
       </c>
       <c r="D245" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8228,13 +8222,13 @@
     </row>
     <row r="246" spans="1:7">
       <c r="A246" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C246" t="s">
         <v>500</v>
       </c>
       <c r="D246" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8248,13 +8242,16 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" t="s">
-        <v>248</v>
+        <v>250</v>
+      </c>
+      <c r="B247" t="s">
+        <v>493</v>
       </c>
       <c r="C247" t="s">
         <v>500</v>
       </c>
       <c r="D247" t="s">
-        <v>737</v>
+        <v>628</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8268,13 +8265,16 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" t="s">
-        <v>249</v>
+        <v>251</v>
+      </c>
+      <c r="B248" t="s">
+        <v>494</v>
       </c>
       <c r="C248" t="s">
         <v>500</v>
       </c>
       <c r="D248" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8288,16 +8288,16 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B249" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C249" t="s">
         <v>500</v>
       </c>
       <c r="D249" t="s">
-        <v>628</v>
+        <v>658</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8311,16 +8311,13 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" t="s">
-        <v>251</v>
-      </c>
-      <c r="B250" t="s">
-        <v>494</v>
+        <v>253</v>
       </c>
       <c r="C250" t="s">
         <v>500</v>
       </c>
       <c r="D250" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8334,16 +8331,13 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" t="s">
-        <v>252</v>
-      </c>
-      <c r="B251" t="s">
-        <v>495</v>
+        <v>254</v>
       </c>
       <c r="C251" t="s">
         <v>500</v>
       </c>
       <c r="D251" t="s">
-        <v>658</v>
+        <v>741</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8357,13 +8351,13 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C252" t="s">
         <v>500</v>
       </c>
       <c r="D252" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8377,13 +8371,16 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" t="s">
-        <v>254</v>
+        <v>256</v>
+      </c>
+      <c r="B253" t="s">
+        <v>496</v>
       </c>
       <c r="C253" t="s">
         <v>500</v>
       </c>
       <c r="D253" t="s">
-        <v>741</v>
+        <v>501</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8397,13 +8394,16 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" t="s">
-        <v>255</v>
+        <v>257</v>
+      </c>
+      <c r="B254" t="s">
+        <v>497</v>
       </c>
       <c r="C254" t="s">
         <v>500</v>
       </c>
       <c r="D254" t="s">
-        <v>742</v>
+        <v>589</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8417,16 +8417,16 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B255" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C255" t="s">
         <v>500</v>
       </c>
       <c r="D255" t="s">
-        <v>501</v>
+        <v>590</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8440,16 +8440,16 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B256" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C256" t="s">
         <v>500</v>
       </c>
       <c r="D256" t="s">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8463,22 +8463,22 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" t="s">
-        <v>258</v>
+        <v>7</v>
       </c>
       <c r="B257" t="s">
-        <v>498</v>
+        <v>260</v>
       </c>
       <c r="C257" t="s">
         <v>500</v>
       </c>
       <c r="D257" t="s">
-        <v>590</v>
+        <v>501</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>2496</v>
       </c>
       <c r="F257" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G257" t="s">
         <v>745</v>
@@ -8486,22 +8486,22 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" t="s">
-        <v>259</v>
+        <v>8</v>
       </c>
       <c r="B258" t="s">
-        <v>499</v>
+        <v>261</v>
       </c>
       <c r="C258" t="s">
         <v>500</v>
       </c>
       <c r="D258" t="s">
-        <v>627</v>
+        <v>502</v>
       </c>
       <c r="E258">
         <v>0</v>
       </c>
       <c r="F258" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G258" t="s">
         <v>745</v>
@@ -8509,19 +8509,19 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B259" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C259" t="s">
         <v>500</v>
       </c>
       <c r="D259" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E259">
-        <v>2496</v>
+        <v>0</v>
       </c>
       <c r="F259" t="s">
         <v>744</v>
@@ -8532,16 +8532,16 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C260" t="s">
         <v>500</v>
       </c>
       <c r="D260" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8555,16 +8555,16 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B261" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C261" t="s">
         <v>500</v>
       </c>
       <c r="D261" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -8578,16 +8578,16 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C262" t="s">
         <v>500</v>
       </c>
       <c r="D262" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -8601,16 +8601,16 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B263" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C263" t="s">
         <v>500</v>
       </c>
       <c r="D263" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8624,16 +8624,16 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B264" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C264" t="s">
         <v>500</v>
       </c>
       <c r="D264" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8647,16 +8647,16 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B265" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C265" t="s">
         <v>500</v>
       </c>
       <c r="D265" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8670,16 +8670,16 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C266" t="s">
         <v>500</v>
       </c>
       <c r="D266" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8693,16 +8693,16 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B267" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C267" t="s">
         <v>500</v>
       </c>
       <c r="D267" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8716,16 +8716,16 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B268" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C268" t="s">
         <v>500</v>
       </c>
       <c r="D268" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8739,16 +8739,16 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B269" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C269" t="s">
         <v>500</v>
       </c>
       <c r="D269" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8762,19 +8762,19 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B270" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C270" t="s">
         <v>500</v>
       </c>
       <c r="D270" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E270">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="F270" t="s">
         <v>744</v>
@@ -8785,19 +8785,19 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B271" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C271" t="s">
         <v>500</v>
       </c>
       <c r="D271" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E271">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F271" t="s">
         <v>744</v>
@@ -8808,19 +8808,19 @@
     </row>
     <row r="272" spans="1:7">
       <c r="A272" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B272" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C272" t="s">
         <v>500</v>
       </c>
       <c r="D272" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E272">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="F272" t="s">
         <v>744</v>
@@ -8831,19 +8831,19 @@
     </row>
     <row r="273" spans="1:7">
       <c r="A273" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B273" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C273" t="s">
         <v>500</v>
       </c>
       <c r="D273" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E273">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F273" t="s">
         <v>744</v>
@@ -8854,16 +8854,16 @@
     </row>
     <row r="274" spans="1:7">
       <c r="A274" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B274" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C274" t="s">
         <v>500</v>
       </c>
       <c r="D274" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -8877,16 +8877,16 @@
     </row>
     <row r="275" spans="1:7">
       <c r="A275" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B275" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C275" t="s">
         <v>500</v>
       </c>
       <c r="D275" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -8900,16 +8900,16 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B276" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C276" t="s">
         <v>500</v>
       </c>
       <c r="D276" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -8923,16 +8923,16 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B277" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C277" t="s">
         <v>500</v>
       </c>
       <c r="D277" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -8946,16 +8946,16 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B278" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C278" t="s">
         <v>500</v>
       </c>
       <c r="D278" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -8969,16 +8969,16 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B279" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C279" t="s">
         <v>500</v>
       </c>
       <c r="D279" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -8992,16 +8992,16 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B280" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C280" t="s">
         <v>500</v>
       </c>
       <c r="D280" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9015,16 +9015,16 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B281" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C281" t="s">
         <v>500</v>
       </c>
       <c r="D281" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9038,16 +9038,16 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B282" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C282" t="s">
         <v>500</v>
       </c>
       <c r="D282" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9061,16 +9061,16 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B283" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C283" t="s">
         <v>500</v>
       </c>
       <c r="D283" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9084,16 +9084,16 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B284" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C284" t="s">
         <v>500</v>
       </c>
       <c r="D284" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9107,16 +9107,16 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B285" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C285" t="s">
         <v>500</v>
       </c>
       <c r="D285" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9130,16 +9130,16 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B286" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C286" t="s">
         <v>500</v>
       </c>
       <c r="D286" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9153,16 +9153,16 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B287" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C287" t="s">
         <v>500</v>
       </c>
       <c r="D287" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9176,16 +9176,16 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B288" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C288" t="s">
         <v>500</v>
       </c>
       <c r="D288" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9199,16 +9199,16 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B289" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C289" t="s">
         <v>500</v>
       </c>
       <c r="D289" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9222,16 +9222,16 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B290" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C290" t="s">
         <v>500</v>
       </c>
       <c r="D290" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9245,16 +9245,16 @@
     </row>
     <row r="291" spans="1:7">
       <c r="A291" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B291" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C291" t="s">
         <v>500</v>
       </c>
       <c r="D291" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9268,16 +9268,16 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B292" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C292" t="s">
         <v>500</v>
       </c>
       <c r="D292" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9291,16 +9291,16 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B293" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C293" t="s">
         <v>500</v>
       </c>
       <c r="D293" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -9314,16 +9314,16 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B294" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C294" t="s">
         <v>500</v>
       </c>
       <c r="D294" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -9337,16 +9337,16 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B295" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C295" t="s">
         <v>500</v>
       </c>
       <c r="D295" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -9360,16 +9360,16 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B296" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C296" t="s">
         <v>500</v>
       </c>
       <c r="D296" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -9383,16 +9383,16 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B297" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C297" t="s">
         <v>500</v>
       </c>
       <c r="D297" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -9406,16 +9406,16 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B298" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C298" t="s">
         <v>500</v>
       </c>
       <c r="D298" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E298">
         <v>0</v>
@@ -9429,16 +9429,16 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B299" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C299" t="s">
         <v>500</v>
       </c>
       <c r="D299" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -9452,16 +9452,16 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B300" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C300" t="s">
         <v>500</v>
       </c>
       <c r="D300" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -9475,16 +9475,16 @@
     </row>
     <row r="301" spans="1:7">
       <c r="A301" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B301" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C301" t="s">
         <v>500</v>
       </c>
       <c r="D301" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E301">
         <v>0</v>
@@ -9498,16 +9498,16 @@
     </row>
     <row r="302" spans="1:7">
       <c r="A302" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B302" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C302" t="s">
         <v>500</v>
       </c>
       <c r="D302" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E302">
         <v>0</v>
@@ -9521,16 +9521,16 @@
     </row>
     <row r="303" spans="1:7">
       <c r="A303" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B303" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C303" t="s">
         <v>500</v>
       </c>
       <c r="D303" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E303">
         <v>0</v>
@@ -9544,16 +9544,16 @@
     </row>
     <row r="304" spans="1:7">
       <c r="A304" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B304" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C304" t="s">
         <v>500</v>
       </c>
       <c r="D304" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E304">
         <v>0</v>
@@ -9567,16 +9567,16 @@
     </row>
     <row r="305" spans="1:7">
       <c r="A305" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B305" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C305" t="s">
         <v>500</v>
       </c>
       <c r="D305" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E305">
         <v>0</v>
@@ -9590,16 +9590,16 @@
     </row>
     <row r="306" spans="1:7">
       <c r="A306" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B306" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C306" t="s">
         <v>500</v>
       </c>
       <c r="D306" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E306">
         <v>0</v>
@@ -9613,16 +9613,16 @@
     </row>
     <row r="307" spans="1:7">
       <c r="A307" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B307" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C307" t="s">
         <v>500</v>
       </c>
       <c r="D307" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="E307">
         <v>0</v>
@@ -9636,16 +9636,16 @@
     </row>
     <row r="308" spans="1:7">
       <c r="A308" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B308" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C308" t="s">
         <v>500</v>
       </c>
       <c r="D308" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -9659,16 +9659,16 @@
     </row>
     <row r="309" spans="1:7">
       <c r="A309" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B309" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C309" t="s">
         <v>500</v>
       </c>
       <c r="D309" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -9682,16 +9682,16 @@
     </row>
     <row r="310" spans="1:7">
       <c r="A310" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B310" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C310" t="s">
         <v>500</v>
       </c>
       <c r="D310" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -9705,16 +9705,16 @@
     </row>
     <row r="311" spans="1:7">
       <c r="A311" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B311" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C311" t="s">
         <v>500</v>
       </c>
       <c r="D311" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -9728,16 +9728,16 @@
     </row>
     <row r="312" spans="1:7">
       <c r="A312" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B312" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C312" t="s">
         <v>500</v>
       </c>
       <c r="D312" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E312">
         <v>0</v>
@@ -9751,19 +9751,19 @@
     </row>
     <row r="313" spans="1:7">
       <c r="A313" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B313" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C313" t="s">
         <v>500</v>
       </c>
       <c r="D313" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="E313">
-        <v>0</v>
+        <v>2010</v>
       </c>
       <c r="F313" t="s">
         <v>744</v>
@@ -9774,16 +9774,16 @@
     </row>
     <row r="314" spans="1:7">
       <c r="A314" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B314" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C314" t="s">
         <v>500</v>
       </c>
       <c r="D314" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E314">
         <v>0</v>
@@ -9797,19 +9797,19 @@
     </row>
     <row r="315" spans="1:7">
       <c r="A315" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B315" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C315" t="s">
         <v>500</v>
       </c>
       <c r="D315" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E315">
-        <v>2010</v>
+        <v>0</v>
       </c>
       <c r="F315" t="s">
         <v>744</v>
@@ -9820,16 +9820,16 @@
     </row>
     <row r="316" spans="1:7">
       <c r="A316" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B316" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C316" t="s">
         <v>500</v>
       </c>
       <c r="D316" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E316">
         <v>0</v>
@@ -9843,16 +9843,16 @@
     </row>
     <row r="317" spans="1:7">
       <c r="A317" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B317" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C317" t="s">
         <v>500</v>
       </c>
       <c r="D317" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E317">
         <v>0</v>
@@ -9866,16 +9866,16 @@
     </row>
     <row r="318" spans="1:7">
       <c r="A318" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B318" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C318" t="s">
         <v>500</v>
       </c>
       <c r="D318" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E318">
         <v>0</v>
@@ -9889,16 +9889,16 @@
     </row>
     <row r="319" spans="1:7">
       <c r="A319" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B319" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C319" t="s">
         <v>500</v>
       </c>
       <c r="D319" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E319">
         <v>0</v>
@@ -9912,16 +9912,16 @@
     </row>
     <row r="320" spans="1:7">
       <c r="A320" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B320" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C320" t="s">
         <v>500</v>
       </c>
       <c r="D320" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E320">
         <v>0</v>
@@ -9935,16 +9935,16 @@
     </row>
     <row r="321" spans="1:7">
       <c r="A321" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B321" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C321" t="s">
         <v>500</v>
       </c>
       <c r="D321" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E321">
         <v>0</v>
@@ -9958,16 +9958,16 @@
     </row>
     <row r="322" spans="1:7">
       <c r="A322" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B322" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C322" t="s">
         <v>500</v>
       </c>
       <c r="D322" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="E322">
         <v>0</v>
@@ -9981,16 +9981,16 @@
     </row>
     <row r="323" spans="1:7">
       <c r="A323" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B323" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C323" t="s">
         <v>500</v>
       </c>
       <c r="D323" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E323">
         <v>0</v>
@@ -10004,16 +10004,16 @@
     </row>
     <row r="324" spans="1:7">
       <c r="A324" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B324" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C324" t="s">
         <v>500</v>
       </c>
       <c r="D324" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="E324">
         <v>0</v>
@@ -10027,16 +10027,16 @@
     </row>
     <row r="325" spans="1:7">
       <c r="A325" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B325" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C325" t="s">
         <v>500</v>
       </c>
       <c r="D325" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E325">
         <v>0</v>
@@ -10050,16 +10050,16 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B326" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C326" t="s">
         <v>500</v>
       </c>
       <c r="D326" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E326">
         <v>0</v>
@@ -10073,16 +10073,16 @@
     </row>
     <row r="327" spans="1:7">
       <c r="A327" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B327" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C327" t="s">
         <v>500</v>
       </c>
       <c r="D327" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E327">
         <v>0</v>
@@ -10096,16 +10096,16 @@
     </row>
     <row r="328" spans="1:7">
       <c r="A328" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B328" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C328" t="s">
         <v>500</v>
       </c>
       <c r="D328" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E328">
         <v>0</v>
@@ -10119,16 +10119,16 @@
     </row>
     <row r="329" spans="1:7">
       <c r="A329" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B329" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C329" t="s">
         <v>500</v>
       </c>
       <c r="D329" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E329">
         <v>0</v>
@@ -10142,16 +10142,16 @@
     </row>
     <row r="330" spans="1:7">
       <c r="A330" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B330" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C330" t="s">
         <v>500</v>
       </c>
       <c r="D330" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -10165,16 +10165,16 @@
     </row>
     <row r="331" spans="1:7">
       <c r="A331" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B331" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C331" t="s">
         <v>500</v>
       </c>
       <c r="D331" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -10188,16 +10188,16 @@
     </row>
     <row r="332" spans="1:7">
       <c r="A332" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B332" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C332" t="s">
         <v>500</v>
       </c>
       <c r="D332" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -10211,16 +10211,16 @@
     </row>
     <row r="333" spans="1:7">
       <c r="A333" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B333" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C333" t="s">
         <v>500</v>
       </c>
       <c r="D333" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -10234,16 +10234,16 @@
     </row>
     <row r="334" spans="1:7">
       <c r="A334" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B334" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C334" t="s">
         <v>500</v>
       </c>
       <c r="D334" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -10257,16 +10257,16 @@
     </row>
     <row r="335" spans="1:7">
       <c r="A335" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B335" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C335" t="s">
         <v>500</v>
       </c>
       <c r="D335" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -10280,16 +10280,16 @@
     </row>
     <row r="336" spans="1:7">
       <c r="A336" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B336" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C336" t="s">
         <v>500</v>
       </c>
       <c r="D336" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E336">
         <v>0</v>
@@ -10303,16 +10303,16 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B337" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C337" t="s">
         <v>500</v>
       </c>
       <c r="D337" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -10326,16 +10326,16 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B338" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C338" t="s">
         <v>500</v>
       </c>
       <c r="D338" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -10349,16 +10349,16 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B339" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C339" t="s">
         <v>500</v>
       </c>
       <c r="D339" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E339">
         <v>0</v>
@@ -10372,16 +10372,16 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B340" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C340" t="s">
         <v>500</v>
       </c>
       <c r="D340" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E340">
         <v>0</v>
@@ -10395,16 +10395,16 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B341" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C341" t="s">
         <v>500</v>
       </c>
       <c r="D341" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E341">
         <v>0</v>
@@ -10418,16 +10418,16 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B342" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C342" t="s">
         <v>500</v>
       </c>
       <c r="D342" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E342">
         <v>0</v>
@@ -10441,19 +10441,19 @@
     </row>
     <row r="343" spans="1:7">
       <c r="A343" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B343" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C343" t="s">
         <v>500</v>
       </c>
       <c r="D343" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="E343">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F343" t="s">
         <v>744</v>
@@ -10464,16 +10464,16 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B344" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C344" t="s">
         <v>500</v>
       </c>
       <c r="D344" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E344">
         <v>0</v>
@@ -10487,19 +10487,19 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B345" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C345" t="s">
         <v>500</v>
       </c>
       <c r="D345" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E345">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F345" t="s">
         <v>744</v>
@@ -10510,16 +10510,16 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B346" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C346" t="s">
         <v>500</v>
       </c>
       <c r="D346" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E346">
         <v>0</v>
@@ -10533,19 +10533,19 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B347" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C347" t="s">
         <v>500</v>
       </c>
       <c r="D347" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E347">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="F347" t="s">
         <v>744</v>
@@ -10556,16 +10556,16 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B348" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C348" t="s">
         <v>500</v>
       </c>
       <c r="D348" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E348">
         <v>0</v>
@@ -10579,19 +10579,19 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B349" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C349" t="s">
         <v>500</v>
       </c>
       <c r="D349" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="E349">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="F349" t="s">
         <v>744</v>
@@ -10602,16 +10602,16 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B350" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C350" t="s">
         <v>500</v>
       </c>
       <c r="D350" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E350">
         <v>0</v>
@@ -10625,16 +10625,16 @@
     </row>
     <row r="351" spans="1:7">
       <c r="A351" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B351" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C351" t="s">
         <v>500</v>
       </c>
       <c r="D351" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E351">
         <v>0</v>
@@ -10648,16 +10648,16 @@
     </row>
     <row r="352" spans="1:7">
       <c r="A352" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B352" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C352" t="s">
         <v>500</v>
       </c>
       <c r="D352" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E352">
         <v>0</v>
@@ -10671,16 +10671,16 @@
     </row>
     <row r="353" spans="1:7">
       <c r="A353" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B353" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C353" t="s">
         <v>500</v>
       </c>
       <c r="D353" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E353">
         <v>0</v>
@@ -10694,16 +10694,16 @@
     </row>
     <row r="354" spans="1:7">
       <c r="A354" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B354" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C354" t="s">
         <v>500</v>
       </c>
       <c r="D354" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E354">
         <v>0</v>
@@ -10717,16 +10717,16 @@
     </row>
     <row r="355" spans="1:7">
       <c r="A355" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B355" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C355" t="s">
         <v>500</v>
       </c>
       <c r="D355" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E355">
         <v>0</v>
@@ -10740,19 +10740,19 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B356" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C356" t="s">
         <v>500</v>
       </c>
       <c r="D356" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E356">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F356" t="s">
         <v>744</v>
@@ -10763,16 +10763,16 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B357" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C357" t="s">
         <v>500</v>
       </c>
       <c r="D357" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E357">
         <v>0</v>
@@ -10786,16 +10786,16 @@
     </row>
     <row r="358" spans="1:7">
       <c r="A358" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B358" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C358" t="s">
         <v>500</v>
       </c>
       <c r="D358" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E358">
         <v>1000</v>
@@ -10809,16 +10809,16 @@
     </row>
     <row r="359" spans="1:7">
       <c r="A359" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B359" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C359" t="s">
         <v>500</v>
       </c>
       <c r="D359" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E359">
         <v>0</v>
@@ -10832,19 +10832,19 @@
     </row>
     <row r="360" spans="1:7">
       <c r="A360" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B360" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C360" t="s">
         <v>500</v>
       </c>
       <c r="D360" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E360">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F360" t="s">
         <v>744</v>
@@ -10855,16 +10855,16 @@
     </row>
     <row r="361" spans="1:7">
       <c r="A361" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B361" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C361" t="s">
         <v>500</v>
       </c>
       <c r="D361" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E361">
         <v>0</v>
@@ -10878,16 +10878,16 @@
     </row>
     <row r="362" spans="1:7">
       <c r="A362" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B362" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C362" t="s">
         <v>500</v>
       </c>
       <c r="D362" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E362">
         <v>0</v>
@@ -10901,16 +10901,16 @@
     </row>
     <row r="363" spans="1:7">
       <c r="A363" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B363" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C363" t="s">
         <v>500</v>
       </c>
       <c r="D363" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E363">
         <v>0</v>
@@ -10924,16 +10924,16 @@
     </row>
     <row r="364" spans="1:7">
       <c r="A364" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B364" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C364" t="s">
         <v>500</v>
       </c>
       <c r="D364" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E364">
         <v>0</v>
@@ -10947,16 +10947,16 @@
     </row>
     <row r="365" spans="1:7">
       <c r="A365" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B365" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C365" t="s">
         <v>500</v>
       </c>
       <c r="D365" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E365">
         <v>0</v>
@@ -10970,16 +10970,16 @@
     </row>
     <row r="366" spans="1:7">
       <c r="A366" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B366" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C366" t="s">
         <v>500</v>
       </c>
       <c r="D366" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E366">
         <v>0</v>
@@ -10993,16 +10993,16 @@
     </row>
     <row r="367" spans="1:7">
       <c r="A367" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B367" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C367" t="s">
         <v>500</v>
       </c>
       <c r="D367" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E367">
         <v>0</v>
@@ -11016,16 +11016,16 @@
     </row>
     <row r="368" spans="1:7">
       <c r="A368" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B368" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C368" t="s">
         <v>500</v>
       </c>
       <c r="D368" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E368">
         <v>0</v>
@@ -11039,16 +11039,16 @@
     </row>
     <row r="369" spans="1:7">
       <c r="A369" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B369" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C369" t="s">
         <v>500</v>
       </c>
       <c r="D369" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E369">
         <v>0</v>
@@ -11062,16 +11062,16 @@
     </row>
     <row r="370" spans="1:7">
       <c r="A370" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B370" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C370" t="s">
         <v>500</v>
       </c>
       <c r="D370" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E370">
         <v>0</v>
@@ -11085,16 +11085,16 @@
     </row>
     <row r="371" spans="1:7">
       <c r="A371" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B371" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C371" t="s">
         <v>500</v>
       </c>
       <c r="D371" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E371">
         <v>0</v>
@@ -11108,19 +11108,19 @@
     </row>
     <row r="372" spans="1:7">
       <c r="A372" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B372" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C372" t="s">
         <v>500</v>
       </c>
       <c r="D372" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E372">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F372" t="s">
         <v>744</v>
@@ -11131,16 +11131,16 @@
     </row>
     <row r="373" spans="1:7">
       <c r="A373" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B373" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C373" t="s">
         <v>500</v>
       </c>
       <c r="D373" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E373">
         <v>0</v>
@@ -11154,19 +11154,19 @@
     </row>
     <row r="374" spans="1:7">
       <c r="A374" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B374" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C374" t="s">
         <v>500</v>
       </c>
       <c r="D374" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E374">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F374" t="s">
         <v>744</v>
@@ -11177,16 +11177,16 @@
     </row>
     <row r="375" spans="1:7">
       <c r="A375" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B375" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C375" t="s">
         <v>500</v>
       </c>
       <c r="D375" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E375">
         <v>0</v>
@@ -11200,16 +11200,16 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B376" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C376" t="s">
         <v>500</v>
       </c>
       <c r="D376" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E376">
         <v>0</v>
@@ -11223,16 +11223,16 @@
     </row>
     <row r="377" spans="1:7">
       <c r="A377" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B377" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C377" t="s">
         <v>500</v>
       </c>
       <c r="D377" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E377">
         <v>0</v>
@@ -11246,16 +11246,16 @@
     </row>
     <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B378" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C378" t="s">
         <v>500</v>
       </c>
       <c r="D378" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E378">
         <v>0</v>
@@ -11269,16 +11269,16 @@
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B379" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C379" t="s">
         <v>500</v>
       </c>
       <c r="D379" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E379">
         <v>0</v>
@@ -11292,16 +11292,16 @@
     </row>
     <row r="380" spans="1:7">
       <c r="A380" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B380" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C380" t="s">
         <v>500</v>
       </c>
       <c r="D380" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E380">
         <v>0</v>
@@ -11315,16 +11315,16 @@
     </row>
     <row r="381" spans="1:7">
       <c r="A381" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B381" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C381" t="s">
         <v>500</v>
       </c>
       <c r="D381" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E381">
         <v>0</v>
@@ -11338,19 +11338,19 @@
     </row>
     <row r="382" spans="1:7">
       <c r="A382" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B382" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C382" t="s">
         <v>500</v>
       </c>
       <c r="D382" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E382">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F382" t="s">
         <v>744</v>
@@ -11361,16 +11361,16 @@
     </row>
     <row r="383" spans="1:7">
       <c r="A383" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B383" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C383" t="s">
         <v>500</v>
       </c>
       <c r="D383" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E383">
         <v>0</v>
@@ -11384,19 +11384,19 @@
     </row>
     <row r="384" spans="1:7">
       <c r="A384" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B384" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C384" t="s">
         <v>500</v>
       </c>
       <c r="D384" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="E384">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F384" t="s">
         <v>744</v>
@@ -11407,16 +11407,16 @@
     </row>
     <row r="385" spans="1:7">
       <c r="A385" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B385" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C385" t="s">
         <v>500</v>
       </c>
       <c r="D385" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E385">
         <v>0</v>
@@ -11430,16 +11430,16 @@
     </row>
     <row r="386" spans="1:7">
       <c r="A386" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B386" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C386" t="s">
         <v>500</v>
       </c>
       <c r="D386" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="E386">
         <v>0</v>
@@ -11453,16 +11453,16 @@
     </row>
     <row r="387" spans="1:7">
       <c r="A387" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B387" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C387" t="s">
         <v>500</v>
       </c>
       <c r="D387" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E387">
         <v>0</v>
@@ -11476,16 +11476,16 @@
     </row>
     <row r="388" spans="1:7">
       <c r="A388" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B388" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C388" t="s">
         <v>500</v>
       </c>
       <c r="D388" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E388">
         <v>0</v>
@@ -11499,16 +11499,16 @@
     </row>
     <row r="389" spans="1:7">
       <c r="A389" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B389" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C389" t="s">
         <v>500</v>
       </c>
       <c r="D389" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E389">
         <v>0</v>
@@ -11522,16 +11522,16 @@
     </row>
     <row r="390" spans="1:7">
       <c r="A390" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B390" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C390" t="s">
         <v>500</v>
       </c>
       <c r="D390" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E390">
         <v>0</v>
@@ -11545,16 +11545,16 @@
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B391" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C391" t="s">
         <v>500</v>
       </c>
       <c r="D391" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E391">
         <v>0</v>
@@ -11568,16 +11568,16 @@
     </row>
     <row r="392" spans="1:7">
       <c r="A392" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B392" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C392" t="s">
         <v>500</v>
       </c>
       <c r="D392" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E392">
         <v>0</v>
@@ -11591,16 +11591,16 @@
     </row>
     <row r="393" spans="1:7">
       <c r="A393" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B393" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C393" t="s">
         <v>500</v>
       </c>
       <c r="D393" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E393">
         <v>0</v>
@@ -11614,16 +11614,16 @@
     </row>
     <row r="394" spans="1:7">
       <c r="A394" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B394" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C394" t="s">
         <v>500</v>
       </c>
       <c r="D394" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E394">
         <v>0</v>
@@ -11637,16 +11637,16 @@
     </row>
     <row r="395" spans="1:7">
       <c r="A395" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B395" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C395" t="s">
         <v>500</v>
       </c>
       <c r="D395" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E395">
         <v>0</v>
@@ -11660,16 +11660,16 @@
     </row>
     <row r="396" spans="1:7">
       <c r="A396" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B396" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C396" t="s">
         <v>500</v>
       </c>
       <c r="D396" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E396">
         <v>0</v>
@@ -11683,16 +11683,16 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B397" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C397" t="s">
         <v>500</v>
       </c>
       <c r="D397" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="E397">
         <v>0</v>
@@ -11706,19 +11706,19 @@
     </row>
     <row r="398" spans="1:7">
       <c r="A398" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B398" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C398" t="s">
         <v>500</v>
       </c>
       <c r="D398" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E398">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F398" t="s">
         <v>744</v>
@@ -11729,16 +11729,16 @@
     </row>
     <row r="399" spans="1:7">
       <c r="A399" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B399" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C399" t="s">
         <v>500</v>
       </c>
       <c r="D399" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E399">
         <v>0</v>
@@ -11752,19 +11752,19 @@
     </row>
     <row r="400" spans="1:7">
       <c r="A400" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B400" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C400" t="s">
         <v>500</v>
       </c>
       <c r="D400" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E400">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F400" t="s">
         <v>744</v>
@@ -11775,16 +11775,16 @@
     </row>
     <row r="401" spans="1:7">
       <c r="A401" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B401" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C401" t="s">
         <v>500</v>
       </c>
       <c r="D401" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E401">
         <v>0</v>
@@ -11798,16 +11798,16 @@
     </row>
     <row r="402" spans="1:7">
       <c r="A402" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B402" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C402" t="s">
         <v>500</v>
       </c>
       <c r="D402" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E402">
         <v>0</v>
@@ -11821,16 +11821,16 @@
     </row>
     <row r="403" spans="1:7">
       <c r="A403" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B403" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C403" t="s">
         <v>500</v>
       </c>
       <c r="D403" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E403">
         <v>0</v>
@@ -11844,16 +11844,16 @@
     </row>
     <row r="404" spans="1:7">
       <c r="A404" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B404" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C404" t="s">
         <v>500</v>
       </c>
       <c r="D404" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E404">
         <v>0</v>
@@ -11867,16 +11867,16 @@
     </row>
     <row r="405" spans="1:7">
       <c r="A405" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B405" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C405" t="s">
         <v>500</v>
       </c>
       <c r="D405" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E405">
         <v>0</v>
@@ -11890,19 +11890,19 @@
     </row>
     <row r="406" spans="1:7">
       <c r="A406" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B406" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C406" t="s">
         <v>500</v>
       </c>
       <c r="D406" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E406">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="F406" t="s">
         <v>744</v>
@@ -11913,19 +11913,19 @@
     </row>
     <row r="407" spans="1:7">
       <c r="A407" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B407" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C407" t="s">
         <v>500</v>
       </c>
       <c r="D407" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="E407">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="F407" t="s">
         <v>744</v>
@@ -11936,19 +11936,19 @@
     </row>
     <row r="408" spans="1:7">
       <c r="A408" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B408" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C408" t="s">
         <v>500</v>
       </c>
       <c r="D408" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E408">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="F408" t="s">
         <v>744</v>
@@ -11959,19 +11959,19 @@
     </row>
     <row r="409" spans="1:7">
       <c r="A409" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B409" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C409" t="s">
         <v>500</v>
       </c>
       <c r="D409" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E409">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="F409" t="s">
         <v>744</v>
@@ -11982,19 +11982,19 @@
     </row>
     <row r="410" spans="1:7">
       <c r="A410" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B410" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C410" t="s">
         <v>500</v>
       </c>
       <c r="D410" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E410">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="F410" t="s">
         <v>744</v>
@@ -12005,16 +12005,16 @@
     </row>
     <row r="411" spans="1:7">
       <c r="A411" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B411" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C411" t="s">
         <v>500</v>
       </c>
       <c r="D411" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E411">
         <v>0</v>
@@ -12028,19 +12028,19 @@
     </row>
     <row r="412" spans="1:7">
       <c r="A412" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B412" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C412" t="s">
         <v>500</v>
       </c>
       <c r="D412" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E412">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="F412" t="s">
         <v>744</v>
@@ -12051,16 +12051,16 @@
     </row>
     <row r="413" spans="1:7">
       <c r="A413" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B413" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C413" t="s">
         <v>500</v>
       </c>
       <c r="D413" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E413">
         <v>0</v>
@@ -12074,16 +12074,16 @@
     </row>
     <row r="414" spans="1:7">
       <c r="A414" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B414" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C414" t="s">
         <v>500</v>
       </c>
       <c r="D414" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E414">
         <v>0</v>
@@ -12097,16 +12097,16 @@
     </row>
     <row r="415" spans="1:7">
       <c r="A415" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B415" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C415" t="s">
         <v>500</v>
       </c>
       <c r="D415" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E415">
         <v>0</v>
@@ -12120,19 +12120,19 @@
     </row>
     <row r="416" spans="1:7">
       <c r="A416" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B416" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C416" t="s">
         <v>500</v>
       </c>
       <c r="D416" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E416">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="F416" t="s">
         <v>744</v>
@@ -12143,16 +12143,16 @@
     </row>
     <row r="417" spans="1:7">
       <c r="A417" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B417" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C417" t="s">
         <v>500</v>
       </c>
       <c r="D417" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E417">
         <v>0</v>
@@ -12166,19 +12166,19 @@
     </row>
     <row r="418" spans="1:7">
       <c r="A418" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C418" t="s">
         <v>500</v>
       </c>
       <c r="D418" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E418">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="F418" t="s">
         <v>744</v>
@@ -12189,16 +12189,16 @@
     </row>
     <row r="419" spans="1:7">
       <c r="A419" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B419" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C419" t="s">
         <v>500</v>
       </c>
       <c r="D419" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E419">
         <v>0</v>
@@ -12212,16 +12212,16 @@
     </row>
     <row r="420" spans="1:7">
       <c r="A420" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B420" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C420" t="s">
         <v>500</v>
       </c>
       <c r="D420" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="E420">
         <v>0</v>
@@ -12235,16 +12235,16 @@
     </row>
     <row r="421" spans="1:7">
       <c r="A421" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B421" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C421" t="s">
         <v>500</v>
       </c>
       <c r="D421" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="E421">
         <v>0</v>
@@ -12258,16 +12258,16 @@
     </row>
     <row r="422" spans="1:7">
       <c r="A422" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B422" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C422" t="s">
         <v>500</v>
       </c>
       <c r="D422" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E422">
         <v>0</v>
@@ -12281,16 +12281,16 @@
     </row>
     <row r="423" spans="1:7">
       <c r="A423" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B423" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C423" t="s">
         <v>500</v>
       </c>
       <c r="D423" t="s">
-        <v>662</v>
+        <v>615</v>
       </c>
       <c r="E423">
         <v>0</v>
@@ -12304,16 +12304,16 @@
     </row>
     <row r="424" spans="1:7">
       <c r="A424" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B424" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C424" t="s">
         <v>500</v>
       </c>
       <c r="D424" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E424">
         <v>0</v>
@@ -12327,16 +12327,16 @@
     </row>
     <row r="425" spans="1:7">
       <c r="A425" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B425" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C425" t="s">
         <v>500</v>
       </c>
       <c r="D425" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E425">
         <v>0</v>
@@ -12350,16 +12350,16 @@
     </row>
     <row r="426" spans="1:7">
       <c r="A426" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B426" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C426" t="s">
         <v>500</v>
       </c>
       <c r="D426" t="s">
-        <v>615</v>
+        <v>667</v>
       </c>
       <c r="E426">
         <v>0</v>
@@ -12373,19 +12373,19 @@
     </row>
     <row r="427" spans="1:7">
       <c r="A427" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B427" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C427" t="s">
         <v>500</v>
       </c>
       <c r="D427" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="E427">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F427" t="s">
         <v>744</v>
@@ -12396,19 +12396,19 @@
     </row>
     <row r="428" spans="1:7">
       <c r="A428" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B428" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C428" t="s">
         <v>500</v>
       </c>
       <c r="D428" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="E428">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F428" t="s">
         <v>744</v>
@@ -12419,16 +12419,16 @@
     </row>
     <row r="429" spans="1:7">
       <c r="A429" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B429" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C429" t="s">
         <v>500</v>
       </c>
       <c r="D429" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E429">
         <v>0</v>
@@ -12442,19 +12442,19 @@
     </row>
     <row r="430" spans="1:7">
       <c r="A430" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B430" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C430" t="s">
         <v>500</v>
       </c>
       <c r="D430" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E430">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F430" t="s">
         <v>744</v>
@@ -12465,19 +12465,19 @@
     </row>
     <row r="431" spans="1:7">
       <c r="A431" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B431" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C431" t="s">
         <v>500</v>
       </c>
       <c r="D431" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="E431">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="F431" t="s">
         <v>744</v>
@@ -12488,19 +12488,19 @@
     </row>
     <row r="432" spans="1:7">
       <c r="A432" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B432" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C432" t="s">
         <v>500</v>
       </c>
       <c r="D432" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E432">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F432" t="s">
         <v>744</v>
@@ -12511,16 +12511,16 @@
     </row>
     <row r="433" spans="1:7">
       <c r="A433" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B433" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C433" t="s">
         <v>500</v>
       </c>
       <c r="D433" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E433">
         <v>0</v>
@@ -12534,19 +12534,19 @@
     </row>
     <row r="434" spans="1:7">
       <c r="A434" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B434" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C434" t="s">
         <v>500</v>
       </c>
       <c r="D434" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="E434">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F434" t="s">
         <v>744</v>
@@ -12557,19 +12557,19 @@
     </row>
     <row r="435" spans="1:7">
       <c r="A435" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B435" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C435" t="s">
         <v>500</v>
       </c>
       <c r="D435" t="s">
-        <v>673</v>
+        <v>631</v>
       </c>
       <c r="E435">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F435" t="s">
         <v>744</v>
@@ -12580,16 +12580,16 @@
     </row>
     <row r="436" spans="1:7">
       <c r="A436" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B436" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C436" t="s">
         <v>500</v>
       </c>
       <c r="D436" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="E436">
         <v>0</v>
@@ -12603,19 +12603,19 @@
     </row>
     <row r="437" spans="1:7">
       <c r="A437" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B437" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C437" t="s">
         <v>500</v>
       </c>
       <c r="D437" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E437">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F437" t="s">
         <v>744</v>
@@ -12626,19 +12626,19 @@
     </row>
     <row r="438" spans="1:7">
       <c r="A438" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B438" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C438" t="s">
         <v>500</v>
       </c>
       <c r="D438" t="s">
-        <v>631</v>
+        <v>678</v>
       </c>
       <c r="E438">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F438" t="s">
         <v>744</v>
@@ -12649,16 +12649,16 @@
     </row>
     <row r="439" spans="1:7">
       <c r="A439" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B439" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C439" t="s">
         <v>500</v>
       </c>
       <c r="D439" t="s">
-        <v>676</v>
+        <v>622</v>
       </c>
       <c r="E439">
         <v>0</v>
@@ -12672,16 +12672,16 @@
     </row>
     <row r="440" spans="1:7">
       <c r="A440" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B440" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C440" t="s">
         <v>500</v>
       </c>
       <c r="D440" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="E440">
         <v>0</v>
@@ -12695,16 +12695,16 @@
     </row>
     <row r="441" spans="1:7">
       <c r="A441" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B441" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C441" t="s">
         <v>500</v>
       </c>
       <c r="D441" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E441">
         <v>0</v>
@@ -12718,19 +12718,19 @@
     </row>
     <row r="442" spans="1:7">
       <c r="A442" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B442" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C442" t="s">
         <v>500</v>
       </c>
       <c r="D442" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E442">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F442" t="s">
         <v>744</v>
@@ -12741,16 +12741,16 @@
     </row>
     <row r="443" spans="1:7">
       <c r="A443" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B443" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C443" t="s">
         <v>500</v>
       </c>
       <c r="D443" t="s">
-        <v>622</v>
+        <v>682</v>
       </c>
       <c r="E443">
         <v>0</v>
@@ -12764,16 +12764,16 @@
     </row>
     <row r="444" spans="1:7">
       <c r="A444" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B444" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C444" t="s">
         <v>500</v>
       </c>
       <c r="D444" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="E444">
         <v>0</v>
@@ -12787,16 +12787,16 @@
     </row>
     <row r="445" spans="1:7">
       <c r="A445" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B445" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C445" t="s">
         <v>500</v>
       </c>
       <c r="D445" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="E445">
         <v>0</v>
@@ -12810,16 +12810,16 @@
     </row>
     <row r="446" spans="1:7">
       <c r="A446" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B446" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C446" t="s">
         <v>500</v>
       </c>
       <c r="D446" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="E446">
         <v>0</v>
@@ -12833,16 +12833,16 @@
     </row>
     <row r="447" spans="1:7">
       <c r="A447" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B447" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C447" t="s">
         <v>500</v>
       </c>
       <c r="D447" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="E447">
         <v>0</v>
@@ -12856,16 +12856,16 @@
     </row>
     <row r="448" spans="1:7">
       <c r="A448" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B448" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C448" t="s">
         <v>500</v>
       </c>
       <c r="D448" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="E448">
         <v>0</v>
@@ -12879,16 +12879,16 @@
     </row>
     <row r="449" spans="1:7">
       <c r="A449" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B449" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C449" t="s">
         <v>500</v>
       </c>
       <c r="D449" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E449">
         <v>0</v>
@@ -12902,16 +12902,16 @@
     </row>
     <row r="450" spans="1:7">
       <c r="A450" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B450" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C450" t="s">
         <v>500</v>
       </c>
       <c r="D450" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="E450">
         <v>0</v>
@@ -12925,16 +12925,16 @@
     </row>
     <row r="451" spans="1:7">
       <c r="A451" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B451" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C451" t="s">
         <v>500</v>
       </c>
       <c r="D451" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="E451">
         <v>0</v>
@@ -12948,16 +12948,16 @@
     </row>
     <row r="452" spans="1:7">
       <c r="A452" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B452" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C452" t="s">
         <v>500</v>
       </c>
       <c r="D452" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E452">
         <v>0</v>
@@ -12971,16 +12971,16 @@
     </row>
     <row r="453" spans="1:7">
       <c r="A453" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B453" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C453" t="s">
         <v>500</v>
       </c>
       <c r="D453" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E453">
         <v>0</v>
@@ -12994,16 +12994,16 @@
     </row>
     <row r="454" spans="1:7">
       <c r="A454" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B454" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C454" t="s">
         <v>500</v>
       </c>
       <c r="D454" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="E454">
         <v>0</v>
@@ -13017,16 +13017,16 @@
     </row>
     <row r="455" spans="1:7">
       <c r="A455" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B455" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C455" t="s">
         <v>500</v>
       </c>
       <c r="D455" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E455">
         <v>0</v>
@@ -13040,16 +13040,16 @@
     </row>
     <row r="456" spans="1:7">
       <c r="A456" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B456" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C456" t="s">
         <v>500</v>
       </c>
       <c r="D456" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="E456">
         <v>0</v>
@@ -13063,16 +13063,16 @@
     </row>
     <row r="457" spans="1:7">
       <c r="A457" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B457" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C457" t="s">
         <v>500</v>
       </c>
       <c r="D457" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="E457">
         <v>0</v>
@@ -13086,16 +13086,16 @@
     </row>
     <row r="458" spans="1:7">
       <c r="A458" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B458" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C458" t="s">
         <v>500</v>
       </c>
       <c r="D458" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="E458">
         <v>0</v>
@@ -13109,16 +13109,16 @@
     </row>
     <row r="459" spans="1:7">
       <c r="A459" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B459" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C459" t="s">
         <v>500</v>
       </c>
       <c r="D459" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="E459">
         <v>0</v>
@@ -13132,16 +13132,16 @@
     </row>
     <row r="460" spans="1:7">
       <c r="A460" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B460" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C460" t="s">
         <v>500</v>
       </c>
       <c r="D460" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="E460">
         <v>0</v>
@@ -13155,16 +13155,16 @@
     </row>
     <row r="461" spans="1:7">
       <c r="A461" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B461" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C461" t="s">
         <v>500</v>
       </c>
       <c r="D461" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="E461">
         <v>0</v>
@@ -13178,16 +13178,16 @@
     </row>
     <row r="462" spans="1:7">
       <c r="A462" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B462" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C462" t="s">
         <v>500</v>
       </c>
       <c r="D462" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="E462">
         <v>0</v>
@@ -13201,16 +13201,16 @@
     </row>
     <row r="463" spans="1:7">
       <c r="A463" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B463" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C463" t="s">
         <v>500</v>
       </c>
       <c r="D463" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E463">
         <v>0</v>
@@ -13224,16 +13224,16 @@
     </row>
     <row r="464" spans="1:7">
       <c r="A464" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B464" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C464" t="s">
         <v>500</v>
       </c>
       <c r="D464" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="E464">
         <v>0</v>
@@ -13247,16 +13247,16 @@
     </row>
     <row r="465" spans="1:7">
       <c r="A465" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B465" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C465" t="s">
         <v>500</v>
       </c>
       <c r="D465" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E465">
         <v>0</v>
@@ -13270,16 +13270,16 @@
     </row>
     <row r="466" spans="1:7">
       <c r="A466" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B466" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C466" t="s">
         <v>500</v>
       </c>
       <c r="D466" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="E466">
         <v>0</v>
@@ -13293,16 +13293,16 @@
     </row>
     <row r="467" spans="1:7">
       <c r="A467" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B467" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C467" t="s">
         <v>500</v>
       </c>
       <c r="D467" t="s">
-        <v>702</v>
+        <v>632</v>
       </c>
       <c r="E467">
         <v>0</v>
@@ -13316,16 +13316,16 @@
     </row>
     <row r="468" spans="1:7">
       <c r="A468" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B468" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C468" t="s">
         <v>500</v>
       </c>
       <c r="D468" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="E468">
         <v>0</v>
@@ -13339,16 +13339,16 @@
     </row>
     <row r="469" spans="1:7">
       <c r="A469" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B469" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C469" t="s">
         <v>500</v>
       </c>
       <c r="D469" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="E469">
         <v>0</v>
@@ -13362,16 +13362,16 @@
     </row>
     <row r="470" spans="1:7">
       <c r="A470" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B470" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C470" t="s">
         <v>500</v>
       </c>
       <c r="D470" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="E470">
         <v>0</v>
@@ -13385,16 +13385,16 @@
     </row>
     <row r="471" spans="1:7">
       <c r="A471" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B471" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C471" t="s">
         <v>500</v>
       </c>
       <c r="D471" t="s">
-        <v>632</v>
+        <v>709</v>
       </c>
       <c r="E471">
         <v>0</v>
@@ -13408,19 +13408,19 @@
     </row>
     <row r="472" spans="1:7">
       <c r="A472" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B472" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C472" t="s">
         <v>500</v>
       </c>
       <c r="D472" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="E472">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F472" t="s">
         <v>744</v>
@@ -13431,19 +13431,19 @@
     </row>
     <row r="473" spans="1:7">
       <c r="A473" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B473" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C473" t="s">
         <v>500</v>
       </c>
       <c r="D473" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E473">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F473" t="s">
         <v>744</v>
@@ -13454,16 +13454,16 @@
     </row>
     <row r="474" spans="1:7">
       <c r="A474" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B474" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C474" t="s">
         <v>500</v>
       </c>
       <c r="D474" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="E474">
         <v>0</v>
@@ -13477,16 +13477,16 @@
     </row>
     <row r="475" spans="1:7">
       <c r="A475" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B475" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C475" t="s">
         <v>500</v>
       </c>
       <c r="D475" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="E475">
         <v>0</v>
@@ -13500,19 +13500,19 @@
     </row>
     <row r="476" spans="1:7">
       <c r="A476" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B476" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C476" t="s">
         <v>500</v>
       </c>
       <c r="D476" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E476">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F476" t="s">
         <v>744</v>
@@ -13523,19 +13523,19 @@
     </row>
     <row r="477" spans="1:7">
       <c r="A477" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B477" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C477" t="s">
         <v>500</v>
       </c>
       <c r="D477" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="E477">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F477" t="s">
         <v>744</v>
@@ -13546,16 +13546,16 @@
     </row>
     <row r="478" spans="1:7">
       <c r="A478" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B478" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C478" t="s">
         <v>500</v>
       </c>
       <c r="D478" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="E478">
         <v>0</v>
@@ -13569,19 +13569,19 @@
     </row>
     <row r="479" spans="1:7">
       <c r="A479" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B479" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C479" t="s">
         <v>500</v>
       </c>
       <c r="D479" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E479">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F479" t="s">
         <v>744</v>
@@ -13592,19 +13592,19 @@
     </row>
     <row r="480" spans="1:7">
       <c r="A480" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B480" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C480" t="s">
         <v>500</v>
       </c>
       <c r="D480" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="E480">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F480" t="s">
         <v>744</v>
@@ -13615,19 +13615,19 @@
     </row>
     <row r="481" spans="1:7">
       <c r="A481" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B481" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C481" t="s">
         <v>500</v>
       </c>
       <c r="D481" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E481">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F481" t="s">
         <v>744</v>
@@ -13638,19 +13638,19 @@
     </row>
     <row r="482" spans="1:7">
       <c r="A482" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B482" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C482" t="s">
         <v>500</v>
       </c>
       <c r="D482" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E482">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F482" t="s">
         <v>744</v>
@@ -13661,19 +13661,19 @@
     </row>
     <row r="483" spans="1:7">
       <c r="A483" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B483" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C483" t="s">
         <v>500</v>
       </c>
       <c r="D483" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E483">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F483" t="s">
         <v>744</v>
@@ -13684,19 +13684,19 @@
     </row>
     <row r="484" spans="1:7">
       <c r="A484" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B484" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C484" t="s">
         <v>500</v>
       </c>
       <c r="D484" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E484">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F484" t="s">
         <v>744</v>
@@ -13707,19 +13707,19 @@
     </row>
     <row r="485" spans="1:7">
       <c r="A485" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B485" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C485" t="s">
         <v>500</v>
       </c>
       <c r="D485" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="E485">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F485" t="s">
         <v>744</v>
@@ -13730,19 +13730,19 @@
     </row>
     <row r="486" spans="1:7">
       <c r="A486" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B486" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C486" t="s">
         <v>500</v>
       </c>
       <c r="D486" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="E486">
-        <v>50</v>
+        <v>504</v>
       </c>
       <c r="F486" t="s">
         <v>744</v>
@@ -13753,16 +13753,16 @@
     </row>
     <row r="487" spans="1:7">
       <c r="A487" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B487" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C487" t="s">
         <v>500</v>
       </c>
       <c r="D487" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="E487">
         <v>0</v>
@@ -13776,16 +13776,16 @@
     </row>
     <row r="488" spans="1:7">
       <c r="A488" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B488" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C488" t="s">
         <v>500</v>
       </c>
       <c r="D488" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E488">
         <v>0</v>
@@ -13799,16 +13799,16 @@
     </row>
     <row r="489" spans="1:7">
       <c r="A489" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B489" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C489" t="s">
         <v>500</v>
       </c>
       <c r="D489" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E489">
         <v>0</v>
@@ -13822,19 +13822,19 @@
     </row>
     <row r="490" spans="1:7">
       <c r="A490" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B490" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C490" t="s">
         <v>500</v>
       </c>
       <c r="D490" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="E490">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="F490" t="s">
         <v>744</v>
@@ -13845,16 +13845,16 @@
     </row>
     <row r="491" spans="1:7">
       <c r="A491" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B491" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C491" t="s">
         <v>500</v>
       </c>
       <c r="D491" t="s">
-        <v>725</v>
+        <v>670</v>
       </c>
       <c r="E491">
         <v>0</v>
@@ -13868,16 +13868,13 @@
     </row>
     <row r="492" spans="1:7">
       <c r="A492" t="s">
-        <v>236</v>
-      </c>
-      <c r="B492" t="s">
-        <v>489</v>
+        <v>240</v>
       </c>
       <c r="C492" t="s">
         <v>500</v>
       </c>
       <c r="D492" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E492">
         <v>0</v>
@@ -13891,16 +13888,13 @@
     </row>
     <row r="493" spans="1:7">
       <c r="A493" t="s">
-        <v>237</v>
-      </c>
-      <c r="B493" t="s">
-        <v>490</v>
+        <v>241</v>
       </c>
       <c r="C493" t="s">
         <v>500</v>
       </c>
       <c r="D493" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="E493">
         <v>0</v>
@@ -13914,16 +13908,13 @@
     </row>
     <row r="494" spans="1:7">
       <c r="A494" t="s">
-        <v>238</v>
-      </c>
-      <c r="B494" t="s">
-        <v>491</v>
+        <v>242</v>
       </c>
       <c r="C494" t="s">
         <v>500</v>
       </c>
       <c r="D494" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="E494">
         <v>0</v>
@@ -13937,16 +13928,13 @@
     </row>
     <row r="495" spans="1:7">
       <c r="A495" t="s">
-        <v>239</v>
-      </c>
-      <c r="B495" t="s">
-        <v>492</v>
+        <v>243</v>
       </c>
       <c r="C495" t="s">
         <v>500</v>
       </c>
       <c r="D495" t="s">
-        <v>670</v>
+        <v>732</v>
       </c>
       <c r="E495">
         <v>0</v>
@@ -13960,13 +13948,13 @@
     </row>
     <row r="496" spans="1:7">
       <c r="A496" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C496" t="s">
         <v>500</v>
       </c>
       <c r="D496" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="E496">
         <v>0</v>
@@ -13980,13 +13968,13 @@
     </row>
     <row r="497" spans="1:7">
       <c r="A497" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C497" t="s">
         <v>500</v>
       </c>
       <c r="D497" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="E497">
         <v>0</v>
@@ -14000,13 +13988,13 @@
     </row>
     <row r="498" spans="1:7">
       <c r="A498" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C498" t="s">
         <v>500</v>
       </c>
       <c r="D498" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="E498">
         <v>0</v>
@@ -14020,13 +14008,13 @@
     </row>
     <row r="499" spans="1:7">
       <c r="A499" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C499" t="s">
         <v>500</v>
       </c>
       <c r="D499" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="E499">
         <v>0</v>
@@ -14040,13 +14028,13 @@
     </row>
     <row r="500" spans="1:7">
       <c r="A500" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C500" t="s">
         <v>500</v>
       </c>
       <c r="D500" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="E500">
         <v>0</v>
@@ -14060,13 +14048,13 @@
     </row>
     <row r="501" spans="1:7">
       <c r="A501" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C501" t="s">
         <v>500</v>
       </c>
       <c r="D501" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="E501">
         <v>0</v>
@@ -14080,16 +14068,19 @@
     </row>
     <row r="502" spans="1:7">
       <c r="A502" t="s">
-        <v>246</v>
+        <v>250</v>
+      </c>
+      <c r="B502" t="s">
+        <v>493</v>
       </c>
       <c r="C502" t="s">
         <v>500</v>
       </c>
       <c r="D502" t="s">
-        <v>735</v>
+        <v>628</v>
       </c>
       <c r="E502">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="F502" t="s">
         <v>744</v>
@@ -14100,13 +14091,16 @@
     </row>
     <row r="503" spans="1:7">
       <c r="A503" t="s">
-        <v>247</v>
+        <v>251</v>
+      </c>
+      <c r="B503" t="s">
+        <v>494</v>
       </c>
       <c r="C503" t="s">
         <v>500</v>
       </c>
       <c r="D503" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E503">
         <v>0</v>
@@ -14120,13 +14114,16 @@
     </row>
     <row r="504" spans="1:7">
       <c r="A504" t="s">
-        <v>248</v>
+        <v>252</v>
+      </c>
+      <c r="B504" t="s">
+        <v>495</v>
       </c>
       <c r="C504" t="s">
         <v>500</v>
       </c>
       <c r="D504" t="s">
-        <v>737</v>
+        <v>658</v>
       </c>
       <c r="E504">
         <v>0</v>
@@ -14140,16 +14137,16 @@
     </row>
     <row r="505" spans="1:7">
       <c r="A505" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C505" t="s">
         <v>500</v>
       </c>
       <c r="D505" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E505">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F505" t="s">
         <v>744</v>
@@ -14160,19 +14157,16 @@
     </row>
     <row r="506" spans="1:7">
       <c r="A506" t="s">
-        <v>250</v>
-      </c>
-      <c r="B506" t="s">
-        <v>493</v>
+        <v>254</v>
       </c>
       <c r="C506" t="s">
         <v>500</v>
       </c>
       <c r="D506" t="s">
-        <v>628</v>
+        <v>741</v>
       </c>
       <c r="E506">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="F506" t="s">
         <v>744</v>
@@ -14183,19 +14177,16 @@
     </row>
     <row r="507" spans="1:7">
       <c r="A507" t="s">
-        <v>251</v>
-      </c>
-      <c r="B507" t="s">
-        <v>494</v>
+        <v>255</v>
       </c>
       <c r="C507" t="s">
         <v>500</v>
       </c>
       <c r="D507" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E507">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F507" t="s">
         <v>744</v>
@@ -14206,16 +14197,16 @@
     </row>
     <row r="508" spans="1:7">
       <c r="A508" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B508" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C508" t="s">
         <v>500</v>
       </c>
       <c r="D508" t="s">
-        <v>658</v>
+        <v>501</v>
       </c>
       <c r="E508">
         <v>0</v>
@@ -14229,16 +14220,19 @@
     </row>
     <row r="509" spans="1:7">
       <c r="A509" t="s">
-        <v>253</v>
+        <v>257</v>
+      </c>
+      <c r="B509" t="s">
+        <v>497</v>
       </c>
       <c r="C509" t="s">
         <v>500</v>
       </c>
       <c r="D509" t="s">
-        <v>740</v>
+        <v>589</v>
       </c>
       <c r="E509">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F509" t="s">
         <v>744</v>
@@ -14249,13 +14243,16 @@
     </row>
     <row r="510" spans="1:7">
       <c r="A510" t="s">
-        <v>254</v>
+        <v>258</v>
+      </c>
+      <c r="B510" t="s">
+        <v>498</v>
       </c>
       <c r="C510" t="s">
         <v>500</v>
       </c>
       <c r="D510" t="s">
-        <v>741</v>
+        <v>590</v>
       </c>
       <c r="E510">
         <v>0</v>
@@ -14269,113 +14266,24 @@
     </row>
     <row r="511" spans="1:7">
       <c r="A511" t="s">
-        <v>255</v>
+        <v>259</v>
+      </c>
+      <c r="B511" t="s">
+        <v>499</v>
       </c>
       <c r="C511" t="s">
         <v>500</v>
       </c>
       <c r="D511" t="s">
-        <v>742</v>
+        <v>627</v>
       </c>
       <c r="E511">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F511" t="s">
         <v>744</v>
       </c>
       <c r="G511" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="512" spans="1:7">
-      <c r="A512" t="s">
-        <v>256</v>
-      </c>
-      <c r="B512" t="s">
-        <v>496</v>
-      </c>
-      <c r="C512" t="s">
-        <v>500</v>
-      </c>
-      <c r="D512" t="s">
-        <v>501</v>
-      </c>
-      <c r="E512">
-        <v>0</v>
-      </c>
-      <c r="F512" t="s">
-        <v>744</v>
-      </c>
-      <c r="G512" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="513" spans="1:7">
-      <c r="A513" t="s">
-        <v>257</v>
-      </c>
-      <c r="B513" t="s">
-        <v>497</v>
-      </c>
-      <c r="C513" t="s">
-        <v>500</v>
-      </c>
-      <c r="D513" t="s">
-        <v>589</v>
-      </c>
-      <c r="E513">
-        <v>0</v>
-      </c>
-      <c r="F513" t="s">
-        <v>744</v>
-      </c>
-      <c r="G513" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="514" spans="1:7">
-      <c r="A514" t="s">
-        <v>258</v>
-      </c>
-      <c r="B514" t="s">
-        <v>498</v>
-      </c>
-      <c r="C514" t="s">
-        <v>500</v>
-      </c>
-      <c r="D514" t="s">
-        <v>590</v>
-      </c>
-      <c r="E514">
-        <v>0</v>
-      </c>
-      <c r="F514" t="s">
-        <v>744</v>
-      </c>
-      <c r="G514" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="515" spans="1:7">
-      <c r="A515" t="s">
-        <v>259</v>
-      </c>
-      <c r="B515" t="s">
-        <v>499</v>
-      </c>
-      <c r="C515" t="s">
-        <v>500</v>
-      </c>
-      <c r="D515" t="s">
-        <v>627</v>
-      </c>
-      <c r="E515">
-        <v>0</v>
-      </c>
-      <c r="F515" t="s">
-        <v>744</v>
-      </c>
-      <c r="G515" t="s">
         <v>745</v>
       </c>
     </row>
